--- a/product-definitions/spreadsheet/co-concentration.xlsx
+++ b/product-definitions/spreadsheet/co-concentration.xlsx
@@ -1928,7 +1928,7 @@
       <c r="L20" s="8"/>
       <c r="M20" s="7"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
         <v>19</v>
@@ -1945,7 +1945,7 @@
       <c r="L21" s="17"/>
       <c r="M21" s="7"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7" t="s">
         <v>20</v>
@@ -1959,7 +1959,7 @@
       <c r="G22" s="7"/>
       <c r="L22" s="16"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7" t="s">
         <v>22</v>
@@ -1973,7 +1973,7 @@
       <c r="G23" s="7"/>
       <c r="L23" s="16"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7" t="s">
         <v>23</v>
@@ -1987,7 +1987,7 @@
       <c r="G24" s="7"/>
       <c r="L24" s="16"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="7" t="s">
         <v>25</v>
@@ -2001,7 +2001,7 @@
       <c r="G25" s="7"/>
       <c r="L25" s="16"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="7"/>
       <c r="B26" s="8" t="s">
         <v>26</v>
@@ -2015,7 +2015,7 @@
       <c r="G26" s="7"/>
       <c r="L26" s="16"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="7"/>
       <c r="B27" s="7" t="s">
         <v>28</v>
@@ -2029,7 +2029,7 @@
       <c r="G27" s="7"/>
       <c r="L27" s="16"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="7"/>
       <c r="B28" s="18" t="s">
         <v>30</v>
@@ -2043,7 +2043,7 @@
       <c r="G28" s="7"/>
       <c r="L28" s="16"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -2052,7 +2052,7 @@
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
@@ -2063,7 +2063,7 @@
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="7"/>
       <c r="B31" s="7" t="s">
         <v>10</v>
@@ -2076,7 +2076,7 @@
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="7"/>
       <c r="B32" s="7" t="s">
         <v>12</v>
@@ -2089,7 +2089,7 @@
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="8"/>
       <c r="B33" s="8" t="s">
         <v>2</v>
@@ -2102,7 +2102,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="7"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
         <v>19</v>
@@ -2115,7 +2115,7 @@
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="7"/>
       <c r="B35" s="7" t="s">
         <v>20</v>
@@ -2128,7 +2128,7 @@
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="7"/>
       <c r="B36" s="7" t="s">
         <v>22</v>
@@ -2141,7 +2141,7 @@
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="7"/>
       <c r="B37" s="7" t="s">
         <v>23</v>
@@ -2154,7 +2154,7 @@
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="7"/>
       <c r="B38" s="7" t="s">
         <v>25</v>
@@ -2167,7 +2167,7 @@
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="7"/>
       <c r="B39" s="8" t="s">
         <v>26</v>
@@ -2180,7 +2180,7 @@
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="7"/>
       <c r="B40" s="7" t="s">
         <v>28</v>
@@ -2193,7 +2193,7 @@
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="7"/>
       <c r="B41" s="18" t="s">
         <v>30</v>
@@ -2206,7 +2206,7 @@
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -2215,7 +2215,7 @@
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="6" t="s">
         <v>38</v>
       </c>
@@ -2226,7 +2226,7 @@
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="7"/>
       <c r="B44" s="7" t="s">
         <v>10</v>
@@ -2239,7 +2239,7 @@
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="7"/>
       <c r="B45" s="7" t="s">
         <v>12</v>
@@ -2252,7 +2252,7 @@
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="8"/>
       <c r="B46" s="8" t="s">
         <v>2</v>
@@ -2265,7 +2265,7 @@
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="7"/>
       <c r="B47" s="7" t="s">
         <v>19</v>
@@ -2278,7 +2278,7 @@
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="7"/>
       <c r="B48" s="7" t="s">
         <v>20</v>
@@ -2291,7 +2291,7 @@
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="7"/>
       <c r="B49" s="7" t="s">
         <v>22</v>
@@ -2304,7 +2304,7 @@
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="7" t="s">
         <v>23</v>
@@ -2317,7 +2317,7 @@
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="7"/>
       <c r="B51" s="7" t="s">
         <v>25</v>
@@ -2330,7 +2330,7 @@
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="7"/>
       <c r="B52" s="8" t="s">
         <v>26</v>
@@ -2343,7 +2343,7 @@
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="7"/>
       <c r="B53" s="7" t="s">
         <v>28</v>
@@ -2356,7 +2356,7 @@
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="7"/>
       <c r="B54" s="18" t="s">
         <v>30</v>
@@ -2369,7 +2369,7 @@
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -2378,14 +2378,14 @@
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="19"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
         <v>10</v>
@@ -2394,7 +2394,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="2"/>
       <c r="B58" s="2" t="s">
         <v>12</v>
@@ -2403,7 +2403,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="2"/>
       <c r="B59" s="2" t="s">
         <v>2</v>
@@ -2412,14 +2412,14 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C60" s="19"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="2"/>
       <c r="B61" s="2" t="s">
         <v>20</v>
@@ -2428,7 +2428,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="2"/>
       <c r="B62" s="7" t="s">
         <v>44</v>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="D62" s="7"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="2"/>
       <c r="B63" s="9" t="s">
         <v>46</v>
